--- a/liga1_data.xlsx
+++ b/liga1_data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EMPRESA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914515B3-232D-41F8-8354-59F04AA0CFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6DD983-CBBD-403F-B391-D98D9E864661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F65AA1A5-5127-43BD-8A19-36C436C51554}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F65AA1A5-5127-43BD-8A19-36C436C51554}"/>
   </bookViews>
   <sheets>
     <sheet name="Partidos_Fecha" sheetId="5" r:id="rId1"/>
-    <sheet name="Data_Geografica" sheetId="1" r:id="rId2"/>
-    <sheet name="Tabla_Posiciones_Clausura" sheetId="3" r:id="rId3"/>
+    <sheet name="Resultados_Clausura" sheetId="6" r:id="rId2"/>
+    <sheet name="Data_Geografica" sheetId="1" r:id="rId3"/>
+    <sheet name="Tabla_Posiciones_Clausura" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="134">
   <si>
     <t>Club</t>
   </si>
@@ -408,6 +409,36 @@
   </si>
   <si>
     <t>Día</t>
+  </si>
+  <si>
+    <t>Goles_Local</t>
+  </si>
+  <si>
+    <t>Goles_Visita</t>
+  </si>
+  <si>
+    <t>Jornada 1</t>
+  </si>
+  <si>
+    <t>UTC Cajamarca</t>
+  </si>
+  <si>
+    <t>Jornada 2</t>
+  </si>
+  <si>
+    <t>Jornada 3</t>
+  </si>
+  <si>
+    <t>Jornada 4</t>
+  </si>
+  <si>
+    <t>Jornada 5</t>
+  </si>
+  <si>
+    <t>Jornada 6</t>
+  </si>
+  <si>
+    <t>Jornada 7</t>
   </si>
 </sst>
 </file>
@@ -2887,6 +2918,1304 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B8F64D-516C-4995-85D6-A667848076C6}">
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>132</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>97</v>
+      </c>
+      <c r="F57" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>82</v>
+      </c>
+      <c r="F61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C11519-6E48-4677-AE28-76BD43DF1603}">
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3405,7 +4734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE34FE4E-9DB2-4DFF-862E-9CB695231D46}">
   <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
